--- a/information_forms/007_membership_order_information_form--information_forms.xlsx
+++ b/information_forms/007_membership_order_information_form--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'payment_method',_'label':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'payment_method', 'label': 'Card'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bank_transfer',_'label':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'bank_transfer', 'label': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'check',_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'check', 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monthly',_'label':_'month-to-month'}</t>
+          <t>month-to-month</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'monthly', 'label': 'Month-to-Month'}</t>
+          <t>Month-to-Month</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'six_monthly',_'label':_'six-monthly'}</t>
+          <t>six-monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'six_monthly', 'label': 'Six-Monthly'}</t>
+          <t>Six-Monthly</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'annual',_'label':_'annual'}</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'annual', 'label': 'Annual'}</t>
+          <t>Annual</t>
         </is>
       </c>
     </row>
